--- a/relatorios/Mogo/Ticket Medio/03-2026.xlsx
+++ b/relatorios/Mogo/Ticket Medio/03-2026.xlsx
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,20 +465,14 @@
           <t>Mesa</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.442,00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>85.659,28</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>59,40</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>1442</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>85659.28</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>59.4</v>
       </c>
     </row>
     <row r="3">
@@ -486,20 +481,14 @@
           <t>Entrega</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3.593,00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>562.888,02</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>156,66</t>
-        </is>
+      <c r="B3" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>269015.33</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>238.49</v>
       </c>
     </row>
     <row r="4">
@@ -508,22 +497,17 @@
           <t>Balcão</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>800,00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>50.307,11</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>62,88</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>50307.11</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>62.88</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -532,18 +516,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.835</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>698.854,41</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>119,77</t>
-        </is>
+          <t>3.370</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>404981.72</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>120.17</v>
       </c>
     </row>
   </sheetData>
